--- a/exports/HEROMOTOCO_full_report.xlsx
+++ b/exports/HEROMOTOCO_full_report.xlsx
@@ -18,9 +18,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
+    <numFmt numFmtId="166" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="167" formatCode="YYYY-MM-DD"/>
   </numFmts>
   <fonts count="1">
     <font>
@@ -51,10 +53,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -420,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q68"/>
+  <dimension ref="A1:U68"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -509,6 +512,26 @@
           <t>candles_held</t>
         </is>
       </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>expiry</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>reached_expiry</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>rule_trades</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>rule_wins</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -534,28 +557,28 @@
         <v>5.51</v>
       </c>
       <c r="G2" s="1" t="n">
-        <v>44615.55208333334</v>
+        <v>44616.38541666666</v>
       </c>
       <c r="H2" t="n">
-        <v>2507.1</v>
+        <v>2318.45</v>
       </c>
       <c r="I2" t="n">
         <v>2483.478646430984</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>44.16666666666666</v>
+        <v>45</v>
       </c>
       <c r="K2" t="n">
-        <v>3.96</v>
+        <v>-3.86</v>
       </c>
       <c r="L2" t="n">
-        <v>3.35</v>
+        <v>4.28</v>
       </c>
       <c r="M2" t="n">
         <v>2.16</v>
       </c>
       <c r="N2" t="n">
-        <v>3.13</v>
+        <v>6.62</v>
       </c>
       <c r="O2" t="n">
         <v>3.15</v>
@@ -564,7 +587,19 @@
         <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>64</v>
+        <v>65</v>
+      </c>
+      <c r="R2" s="3" t="n">
+        <v>44588</v>
+      </c>
+      <c r="S2" t="b">
+        <v>1</v>
+      </c>
+      <c r="T2" t="n">
+        <v>2</v>
+      </c>
+      <c r="U2" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="3">
@@ -591,19 +626,19 @@
         <v>12.52</v>
       </c>
       <c r="G3" s="1" t="n">
-        <v>44636.55208333334</v>
+        <v>44637.38541666666</v>
       </c>
       <c r="H3" t="n">
-        <v>2212.5</v>
+        <v>2243.95</v>
       </c>
       <c r="I3" t="n">
         <v>2217.925734445934</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>20.16666666666667</v>
+        <v>21</v>
       </c>
       <c r="K3" t="n">
-        <v>4.57</v>
+        <v>3.21</v>
       </c>
       <c r="L3" t="n">
         <v>6.23</v>
@@ -621,7 +656,19 @@
         <v>1</v>
       </c>
       <c r="Q3" t="n">
-        <v>28</v>
+        <v>29</v>
+      </c>
+      <c r="R3" s="3" t="n">
+        <v>44651</v>
+      </c>
+      <c r="S3" t="b">
+        <v>0</v>
+      </c>
+      <c r="T3" t="n">
+        <v>1</v>
+      </c>
+      <c r="U3" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="4">
@@ -648,22 +695,22 @@
         <v>6.79</v>
       </c>
       <c r="G4" s="1" t="n">
-        <v>44649.38541666666</v>
+        <v>44649.55208333334</v>
       </c>
       <c r="H4" t="n">
-        <v>2224.2</v>
+        <v>2067.15</v>
       </c>
       <c r="I4" t="n">
         <v>2123.857308570804</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>12</v>
+        <v>12.16666666666667</v>
       </c>
       <c r="K4" t="n">
-        <v>-0.88</v>
+        <v>-7.88</v>
       </c>
       <c r="L4" t="n">
-        <v>3.11</v>
+        <v>10.66</v>
       </c>
       <c r="M4" t="n">
         <v>1.44</v>
@@ -678,7 +725,19 @@
         <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>15</v>
+        <v>16</v>
+      </c>
+      <c r="R4" s="3" t="n">
+        <v>44651</v>
+      </c>
+      <c r="S4" t="b">
+        <v>0</v>
+      </c>
+      <c r="T4" t="n">
+        <v>1</v>
+      </c>
+      <c r="U4" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -705,28 +764,28 @@
         <v>11.18</v>
       </c>
       <c r="G5" s="1" t="n">
-        <v>44676.55208333334</v>
+        <v>44677.38541666666</v>
       </c>
       <c r="H5" t="n">
-        <v>2135.4</v>
+        <v>2223.2</v>
       </c>
       <c r="I5" t="n">
         <v>2216.668955354476</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>27</v>
+        <v>27.83333333333333</v>
       </c>
       <c r="K5" t="n">
-        <v>-3.3</v>
+        <v>-7.55</v>
       </c>
       <c r="L5" t="n">
-        <v>7.64</v>
+        <v>8.02</v>
       </c>
       <c r="M5" t="n">
         <v>1.46</v>
       </c>
       <c r="N5" t="n">
-        <v>3.08</v>
+        <v>5.16</v>
       </c>
       <c r="O5" t="n">
         <v>-6.9</v>
@@ -735,7 +794,19 @@
         <v>1</v>
       </c>
       <c r="Q5" t="n">
-        <v>35</v>
+        <v>36</v>
+      </c>
+      <c r="R5" s="3" t="n">
+        <v>44651</v>
+      </c>
+      <c r="S5" t="b">
+        <v>1</v>
+      </c>
+      <c r="T5" t="n">
+        <v>2</v>
+      </c>
+      <c r="U5" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="6">
@@ -762,19 +833,19 @@
         <v>7.17</v>
       </c>
       <c r="G6" s="1" t="n">
-        <v>44714.55208333334</v>
+        <v>44715.38541666666</v>
       </c>
       <c r="H6" t="n">
-        <v>2499.85</v>
+        <v>2451.3</v>
       </c>
       <c r="I6" t="n">
         <v>2486.902533278429</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>37.16666666666666</v>
+        <v>38</v>
       </c>
       <c r="K6" t="n">
-        <v>12.44</v>
+        <v>10.26</v>
       </c>
       <c r="L6" t="n">
         <v>3.41</v>
@@ -792,7 +863,19 @@
         <v>1</v>
       </c>
       <c r="Q6" t="n">
-        <v>54</v>
+        <v>55</v>
+      </c>
+      <c r="R6" s="3" t="n">
+        <v>44679</v>
+      </c>
+      <c r="S6" t="b">
+        <v>1</v>
+      </c>
+      <c r="T6" t="n">
+        <v>3</v>
+      </c>
+      <c r="U6" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="7">
@@ -819,28 +902,28 @@
         <v>7.75</v>
       </c>
       <c r="G7" s="1" t="n">
-        <v>44734.55208333334</v>
+        <v>44735.38541666666</v>
       </c>
       <c r="H7" t="n">
-        <v>2361.75</v>
+        <v>2457.35</v>
       </c>
       <c r="I7" t="n">
         <v>2431.779631909841</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>19.16666666666667</v>
+        <v>20</v>
       </c>
       <c r="K7" t="n">
-        <v>3.65</v>
+        <v>-0.25</v>
       </c>
       <c r="L7" t="n">
         <v>3.02</v>
       </c>
       <c r="M7" t="n">
-        <v>0.73</v>
+        <v>2.13</v>
       </c>
       <c r="N7" t="n">
-        <v>1.99</v>
+        <v>6.36</v>
       </c>
       <c r="O7" t="n">
         <v>-3.15</v>
@@ -849,7 +932,19 @@
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>28</v>
+        <v>29</v>
+      </c>
+      <c r="R7" s="3" t="n">
+        <v>44742</v>
+      </c>
+      <c r="S7" t="b">
+        <v>0</v>
+      </c>
+      <c r="T7" t="n">
+        <v>1</v>
+      </c>
+      <c r="U7" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -876,19 +971,19 @@
         <v>6.75</v>
       </c>
       <c r="G8" s="1" t="n">
-        <v>44769.55208333334</v>
+        <v>44770.38541666666</v>
       </c>
       <c r="H8" t="n">
-        <v>2612.95</v>
+        <v>2602.6</v>
       </c>
       <c r="I8" t="n">
         <v>2604.680086049683</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>34.16666666666666</v>
+        <v>35</v>
       </c>
       <c r="K8" t="n">
-        <v>6.33</v>
+        <v>5.91</v>
       </c>
       <c r="L8" t="n">
         <v>1.84</v>
@@ -906,7 +1001,19 @@
         <v>1</v>
       </c>
       <c r="Q8" t="n">
-        <v>50</v>
+        <v>51</v>
+      </c>
+      <c r="R8" s="3" t="n">
+        <v>44742</v>
+      </c>
+      <c r="S8" t="b">
+        <v>1</v>
+      </c>
+      <c r="T8" t="n">
+        <v>2</v>
+      </c>
+      <c r="U8" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="9">
@@ -933,19 +1040,19 @@
         <v>5.26</v>
       </c>
       <c r="G9" s="1" t="n">
-        <v>44789.55208333334</v>
+        <v>44790.38541666666</v>
       </c>
       <c r="H9" t="n">
-        <v>2651.45</v>
+        <v>2705.6</v>
       </c>
       <c r="I9" t="n">
         <v>2704.569730763536</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>19.16666666666667</v>
+        <v>20</v>
       </c>
       <c r="K9" t="n">
-        <v>-1.88</v>
+        <v>-3.96</v>
       </c>
       <c r="L9" t="n">
         <v>5.25</v>
@@ -954,7 +1061,7 @@
         <v>1.77</v>
       </c>
       <c r="N9" t="n">
-        <v>2.26</v>
+        <v>3.28</v>
       </c>
       <c r="O9" t="n">
         <v>-0.13</v>
@@ -963,7 +1070,19 @@
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>24</v>
+        <v>25</v>
+      </c>
+      <c r="R9" s="3" t="n">
+        <v>44798</v>
+      </c>
+      <c r="S9" t="b">
+        <v>0</v>
+      </c>
+      <c r="T9" t="n">
+        <v>1</v>
+      </c>
+      <c r="U9" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -990,25 +1109,25 @@
         <v>5.79</v>
       </c>
       <c r="G10" s="1" t="n">
-        <v>44792.55208333334</v>
+        <v>44795.38541666666</v>
       </c>
       <c r="H10" t="n">
-        <v>2672.55</v>
+        <v>2619.3</v>
       </c>
       <c r="I10" t="n">
         <v>2620.299256853499</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>2.166666666666667</v>
+        <v>5</v>
       </c>
       <c r="K10" t="n">
-        <v>-1.22</v>
+        <v>-3.19</v>
       </c>
       <c r="L10" t="n">
-        <v>2.36</v>
+        <v>3.89</v>
       </c>
       <c r="M10" t="n">
-        <v>0.11</v>
+        <v>0.17</v>
       </c>
       <c r="N10" t="n">
         <v>2.43</v>
@@ -1020,7 +1139,19 @@
         <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>6</v>
+        <v>7</v>
+      </c>
+      <c r="R10" s="3" t="n">
+        <v>44798</v>
+      </c>
+      <c r="S10" t="b">
+        <v>0</v>
+      </c>
+      <c r="T10" t="n">
+        <v>1</v>
+      </c>
+      <c r="U10" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -1047,19 +1178,19 @@
         <v>6.05</v>
       </c>
       <c r="G11" s="1" t="n">
-        <v>44861.55208333334</v>
+        <v>44862.38541666666</v>
       </c>
       <c r="H11" t="n">
-        <v>2457.35</v>
+        <v>2482.55</v>
       </c>
       <c r="I11" t="n">
         <v>2474.362826394389</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>66.16666666666667</v>
+        <v>67</v>
       </c>
       <c r="K11" t="n">
-        <v>6.18</v>
+        <v>5.22</v>
       </c>
       <c r="L11" t="n">
         <v>4.39</v>
@@ -1077,7 +1208,19 @@
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>91</v>
+        <v>92</v>
+      </c>
+      <c r="R11" s="3" t="n">
+        <v>44798</v>
+      </c>
+      <c r="S11" t="b">
+        <v>1</v>
+      </c>
+      <c r="T11" t="n">
+        <v>4</v>
+      </c>
+      <c r="U11" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="12">
@@ -1104,19 +1247,19 @@
         <v>3.75</v>
       </c>
       <c r="G12" s="1" t="n">
-        <v>44903.55208333334</v>
+        <v>44904.38541666666</v>
       </c>
       <c r="H12" t="n">
-        <v>2591.5</v>
+        <v>2582.2</v>
       </c>
       <c r="I12" t="n">
         <v>2587.026001272645</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>41.16666666666666</v>
+        <v>42</v>
       </c>
       <c r="K12" t="n">
-        <v>4.39</v>
+        <v>4.01</v>
       </c>
       <c r="L12" t="n">
         <v>2.77</v>
@@ -1134,7 +1277,19 @@
         <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>58</v>
+        <v>59</v>
+      </c>
+      <c r="R12" s="3" t="n">
+        <v>44889</v>
+      </c>
+      <c r="S12" t="b">
+        <v>1</v>
+      </c>
+      <c r="T12" t="n">
+        <v>2</v>
+      </c>
+      <c r="U12" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="13">
@@ -1161,19 +1316,19 @@
         <v>4.26</v>
       </c>
       <c r="G13" s="1" t="n">
-        <v>44943.38541666666</v>
+        <v>44943.55208333334</v>
       </c>
       <c r="H13" t="n">
-        <v>2580.25</v>
+        <v>2601.6</v>
       </c>
       <c r="I13" t="n">
         <v>2599.40780165029</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>39</v>
+        <v>39.16666666666666</v>
       </c>
       <c r="K13" t="n">
-        <v>0.08</v>
+        <v>-0.75</v>
       </c>
       <c r="L13" t="n">
         <v>2.57</v>
@@ -1191,7 +1346,19 @@
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>55</v>
+        <v>56</v>
+      </c>
+      <c r="R13" s="3" t="n">
+        <v>44924</v>
+      </c>
+      <c r="S13" t="b">
+        <v>1</v>
+      </c>
+      <c r="T13" t="n">
+        <v>2</v>
+      </c>
+      <c r="U13" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="14">
@@ -1218,25 +1385,25 @@
         <v>4.15</v>
       </c>
       <c r="G14" s="1" t="n">
-        <v>44953.55208333334</v>
+        <v>44956.38541666666</v>
       </c>
       <c r="H14" t="n">
-        <v>2571.2</v>
+        <v>2535.4</v>
       </c>
       <c r="I14" t="n">
         <v>2540.203230563889</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>10</v>
+        <v>12.83333333333333</v>
       </c>
       <c r="K14" t="n">
-        <v>-1.17</v>
+        <v>-2.54</v>
       </c>
       <c r="L14" t="n">
-        <v>1.96</v>
+        <v>2.68</v>
       </c>
       <c r="M14" t="n">
-        <v>0.3</v>
+        <v>0.48</v>
       </c>
       <c r="N14" t="n">
         <v>1.94</v>
@@ -1248,7 +1415,19 @@
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>15</v>
+        <v>16</v>
+      </c>
+      <c r="R14" s="3" t="n">
+        <v>44951</v>
+      </c>
+      <c r="S14" t="b">
+        <v>1</v>
+      </c>
+      <c r="T14" t="n">
+        <v>2</v>
+      </c>
+      <c r="U14" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="15">
@@ -1275,19 +1454,19 @@
         <v>5.38</v>
       </c>
       <c r="G15" s="1" t="n">
-        <v>45016.55208333334</v>
+        <v>45019.38541666666</v>
       </c>
       <c r="H15" t="n">
-        <v>2188.4</v>
+        <v>2262.9</v>
       </c>
       <c r="I15" t="n">
         <v>2189.891529901314</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>60.16666666666666</v>
+        <v>63</v>
       </c>
       <c r="K15" t="n">
-        <v>13.69</v>
+        <v>10.75</v>
       </c>
       <c r="L15" t="n">
         <v>4.71</v>
@@ -1296,7 +1475,7 @@
         <v>2.25</v>
       </c>
       <c r="N15" t="n">
-        <v>2.83</v>
+        <v>3.82</v>
       </c>
       <c r="O15" t="n">
         <v>-0.72</v>
@@ -1305,7 +1484,19 @@
         <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>84</v>
+        <v>85</v>
+      </c>
+      <c r="R15" s="3" t="n">
+        <v>44980</v>
+      </c>
+      <c r="S15" t="b">
+        <v>1</v>
+      </c>
+      <c r="T15" t="n">
+        <v>3</v>
+      </c>
+      <c r="U15" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="16">
@@ -1332,19 +1523,19 @@
         <v>5.68</v>
       </c>
       <c r="G16" s="1" t="n">
-        <v>45092.38541666666</v>
+        <v>45092.55208333334</v>
       </c>
       <c r="H16" t="n">
-        <v>2748.85</v>
+        <v>2659.9</v>
       </c>
       <c r="I16" t="n">
         <v>2688.168599574979</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>73</v>
+        <v>73.16666666666667</v>
       </c>
       <c r="K16" t="n">
-        <v>21.47</v>
+        <v>17.54</v>
       </c>
       <c r="L16" t="n">
         <v>2.04</v>
@@ -1362,7 +1553,19 @@
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>99</v>
+        <v>100</v>
+      </c>
+      <c r="R16" s="3" t="n">
+        <v>45043</v>
+      </c>
+      <c r="S16" t="b">
+        <v>1</v>
+      </c>
+      <c r="T16" t="n">
+        <v>3</v>
+      </c>
+      <c r="U16" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="17">
@@ -1389,19 +1592,19 @@
         <v>7.13</v>
       </c>
       <c r="G17" s="1" t="n">
-        <v>45105.55208333334</v>
+        <v>45107.38541666666</v>
       </c>
       <c r="H17" t="n">
-        <v>2661.25</v>
+        <v>2734.75</v>
       </c>
       <c r="I17" t="n">
         <v>2729.290295275808</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>13</v>
+        <v>14.83333333333333</v>
       </c>
       <c r="K17" t="n">
-        <v>-0.05</v>
+        <v>-2.81</v>
       </c>
       <c r="L17" t="n">
         <v>3.84</v>
@@ -1410,7 +1613,7 @@
         <v>0.6</v>
       </c>
       <c r="N17" t="n">
-        <v>2.24</v>
+        <v>2.82</v>
       </c>
       <c r="O17" t="n">
         <v>-3.58</v>
@@ -1419,7 +1622,19 @@
         <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>19</v>
+        <v>20</v>
+      </c>
+      <c r="R17" s="3" t="n">
+        <v>45105</v>
+      </c>
+      <c r="S17" t="b">
+        <v>1</v>
+      </c>
+      <c r="T17" t="n">
+        <v>2</v>
+      </c>
+      <c r="U17" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="18">
@@ -1446,19 +1661,19 @@
         <v>5.71</v>
       </c>
       <c r="G18" s="1" t="n">
-        <v>45138.55208333334</v>
+        <v>45139.38541666666</v>
       </c>
       <c r="H18" t="n">
-        <v>3033.9</v>
+        <v>2903.75</v>
       </c>
       <c r="I18" t="n">
         <v>2911.372923096935</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>31.16666666666667</v>
+        <v>32</v>
       </c>
       <c r="K18" t="n">
-        <v>10.94</v>
+        <v>6.18</v>
       </c>
       <c r="L18" t="n">
         <v>2.44</v>
@@ -1467,7 +1682,7 @@
         <v>1.07</v>
       </c>
       <c r="N18" t="n">
-        <v>1.42</v>
+        <v>3.54</v>
       </c>
       <c r="O18" t="n">
         <v>2.82</v>
@@ -1476,7 +1691,19 @@
         <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>44</v>
+        <v>45</v>
+      </c>
+      <c r="R18" s="3" t="n">
+        <v>45134</v>
+      </c>
+      <c r="S18" t="b">
+        <v>1</v>
+      </c>
+      <c r="T18" t="n">
+        <v>2</v>
+      </c>
+      <c r="U18" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="19">
@@ -1503,19 +1730,19 @@
         <v>7.92</v>
       </c>
       <c r="G19" s="1" t="n">
-        <v>45177.55208333334</v>
+        <v>45180.38541666666</v>
       </c>
       <c r="H19" t="n">
-        <v>2840.7</v>
+        <v>2864.95</v>
       </c>
       <c r="I19" t="n">
         <v>2842.874398158613</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>38.16666666666666</v>
+        <v>41</v>
       </c>
       <c r="K19" t="n">
-        <v>2.17</v>
+        <v>1.34</v>
       </c>
       <c r="L19" t="n">
         <v>5.62</v>
@@ -1533,7 +1760,19 @@
         <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>56</v>
+        <v>57</v>
+      </c>
+      <c r="R19" s="3" t="n">
+        <v>45169</v>
+      </c>
+      <c r="S19" t="b">
+        <v>1</v>
+      </c>
+      <c r="T19" t="n">
+        <v>2</v>
+      </c>
+      <c r="U19" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="20">
@@ -1560,22 +1799,22 @@
         <v>3.5</v>
       </c>
       <c r="G20" s="1" t="n">
-        <v>45194.38541666666</v>
+        <v>45194.55208333334</v>
       </c>
       <c r="H20" t="n">
-        <v>2826.05</v>
+        <v>2802.95</v>
       </c>
       <c r="I20" t="n">
         <v>2817.972497420337</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>14</v>
+        <v>14.16666666666667</v>
       </c>
       <c r="K20" t="n">
-        <v>-1.36</v>
+        <v>-2.16</v>
       </c>
       <c r="L20" t="n">
-        <v>2.07</v>
+        <v>2.33</v>
       </c>
       <c r="M20" t="n">
         <v>0.33</v>
@@ -1590,7 +1829,19 @@
         <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>19</v>
+        <v>20</v>
+      </c>
+      <c r="R20" s="3" t="n">
+        <v>45197</v>
+      </c>
+      <c r="S20" t="b">
+        <v>0</v>
+      </c>
+      <c r="T20" t="n">
+        <v>1</v>
+      </c>
+      <c r="U20" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1617,28 +1868,28 @@
         <v>4.63</v>
       </c>
       <c r="G21" s="1" t="n">
-        <v>45209.55208333334</v>
+        <v>45210.38541666666</v>
       </c>
       <c r="H21" t="n">
-        <v>2801.3</v>
+        <v>2914.1</v>
       </c>
       <c r="I21" t="n">
         <v>2910.138053593988</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>15</v>
+        <v>15.83333333333333</v>
       </c>
       <c r="K21" t="n">
-        <v>0.06</v>
+        <v>-3.97</v>
       </c>
       <c r="L21" t="n">
-        <v>3.37</v>
+        <v>4.18</v>
       </c>
       <c r="M21" t="n">
         <v>0.99</v>
       </c>
       <c r="N21" t="n">
-        <v>2.87</v>
+        <v>4.37</v>
       </c>
       <c r="O21" t="n">
         <v>-1.77</v>
@@ -1647,7 +1898,19 @@
         <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>21</v>
+        <v>22</v>
+      </c>
+      <c r="R21" s="3" t="n">
+        <v>45197</v>
+      </c>
+      <c r="S21" t="b">
+        <v>1</v>
+      </c>
+      <c r="T21" t="n">
+        <v>2</v>
+      </c>
+      <c r="U21" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="22">
@@ -1674,19 +1937,19 @@
         <v>6.45</v>
       </c>
       <c r="G22" s="1" t="n">
-        <v>45222.55208333334</v>
+        <v>45224.38541666666</v>
       </c>
       <c r="H22" t="n">
-        <v>2970.45</v>
+        <v>2917.05</v>
       </c>
       <c r="I22" t="n">
         <v>2941.498567483894</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>12.16666666666667</v>
+        <v>14</v>
       </c>
       <c r="K22" t="n">
-        <v>1.93</v>
+        <v>0.1</v>
       </c>
       <c r="L22" t="n">
         <v>3.34</v>
@@ -1704,7 +1967,19 @@
         <v>1</v>
       </c>
       <c r="Q22" t="n">
-        <v>18</v>
+        <v>19</v>
+      </c>
+      <c r="R22" s="3" t="n">
+        <v>45225</v>
+      </c>
+      <c r="S22" t="b">
+        <v>0</v>
+      </c>
+      <c r="T22" t="n">
+        <v>1</v>
+      </c>
+      <c r="U22" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="23">
@@ -1731,28 +2006,28 @@
         <v>6.4</v>
       </c>
       <c r="G23" s="1" t="n">
-        <v>45245.55208333334</v>
+        <v>45246.38541666666</v>
       </c>
       <c r="H23" t="n">
-        <v>2999.75</v>
+        <v>3073.6</v>
       </c>
       <c r="I23" t="n">
         <v>3023.968861131025</v>
       </c>
       <c r="J23" s="2" t="n">
-        <v>21.16666666666667</v>
+        <v>22</v>
       </c>
       <c r="K23" t="n">
-        <v>-2.84</v>
+        <v>-5.37</v>
       </c>
       <c r="L23" t="n">
-        <v>3.54</v>
+        <v>5.66</v>
       </c>
       <c r="M23" t="n">
         <v>1.67</v>
       </c>
       <c r="N23" t="n">
-        <v>2.64</v>
+        <v>3.54</v>
       </c>
       <c r="O23" t="n">
         <v>-0.17</v>
@@ -1761,7 +2036,19 @@
         <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>31</v>
+        <v>32</v>
+      </c>
+      <c r="R23" s="3" t="n">
+        <v>45225</v>
+      </c>
+      <c r="S23" t="b">
+        <v>1</v>
+      </c>
+      <c r="T23" t="n">
+        <v>2</v>
+      </c>
+      <c r="U23" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="24">
@@ -1788,19 +2075,19 @@
         <v>5.24</v>
       </c>
       <c r="G24" s="1" t="n">
-        <v>45294.55208333334</v>
+        <v>45295.38541666666</v>
       </c>
       <c r="H24" t="n">
-        <v>3799.7</v>
+        <v>3753.85</v>
       </c>
       <c r="I24" t="n">
         <v>3774.721410575761</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>48.16666666666666</v>
+        <v>49</v>
       </c>
       <c r="K24" t="n">
-        <v>23.62</v>
+        <v>22.13</v>
       </c>
       <c r="L24" t="n">
         <v>2.31</v>
@@ -1818,7 +2105,19 @@
         <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>66</v>
+        <v>67</v>
+      </c>
+      <c r="R24" s="3" t="n">
+        <v>45260</v>
+      </c>
+      <c r="S24" t="b">
+        <v>1</v>
+      </c>
+      <c r="T24" t="n">
+        <v>3</v>
+      </c>
+      <c r="U24" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="25">
@@ -1845,28 +2144,28 @@
         <v>5.96</v>
       </c>
       <c r="G25" s="1" t="n">
-        <v>45299.55208333334</v>
+        <v>45300.38541666666</v>
       </c>
       <c r="H25" t="n">
-        <v>3815.15</v>
+        <v>3938.65</v>
       </c>
       <c r="I25" t="n">
         <v>3936.830742649344</v>
       </c>
       <c r="J25" s="2" t="n">
-        <v>4.166666666666667</v>
+        <v>5</v>
       </c>
       <c r="K25" t="n">
-        <v>-1.63</v>
+        <v>-4.92</v>
       </c>
       <c r="L25" t="n">
-        <v>2.65</v>
+        <v>5.22</v>
       </c>
       <c r="M25" t="n">
-        <v>0.72</v>
+        <v>0.95</v>
       </c>
       <c r="N25" t="n">
-        <v>1.09</v>
+        <v>2.92</v>
       </c>
       <c r="O25" t="n">
         <v>-1.28</v>
@@ -1875,7 +2174,19 @@
         <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>6</v>
+        <v>7</v>
+      </c>
+      <c r="R25" s="3" t="n">
+        <v>45316</v>
+      </c>
+      <c r="S25" t="b">
+        <v>0</v>
+      </c>
+      <c r="T25" t="n">
+        <v>1</v>
+      </c>
+      <c r="U25" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="26">
@@ -1902,19 +2213,19 @@
         <v>6.13</v>
       </c>
       <c r="G26" s="1" t="n">
-        <v>45331.55208333334</v>
+        <v>45334.38541666666</v>
       </c>
       <c r="H26" t="n">
-        <v>4690.85</v>
+        <v>4450.4</v>
       </c>
       <c r="I26" t="n">
         <v>4455.584136114929</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>31.16666666666667</v>
+        <v>34</v>
       </c>
       <c r="K26" t="n">
-        <v>19.1</v>
+        <v>12.99</v>
       </c>
       <c r="L26" t="n">
         <v>2.63</v>
@@ -1923,7 +2234,7 @@
         <v>2.06</v>
       </c>
       <c r="N26" t="n">
-        <v>0.8100000000000001</v>
+        <v>4.36</v>
       </c>
       <c r="O26" t="n">
         <v>2.92</v>
@@ -1932,7 +2243,19 @@
         <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>46</v>
+        <v>47</v>
+      </c>
+      <c r="R26" s="3" t="n">
+        <v>45316</v>
+      </c>
+      <c r="S26" t="b">
+        <v>1</v>
+      </c>
+      <c r="T26" t="n">
+        <v>2</v>
+      </c>
+      <c r="U26" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="27">
@@ -1959,28 +2282,28 @@
         <v>9.119999999999999</v>
       </c>
       <c r="G27" s="1" t="n">
-        <v>45352.38541666666</v>
+        <v>45355.38541666666</v>
       </c>
       <c r="H27" t="n">
-        <v>4372</v>
+        <v>4508.1</v>
       </c>
       <c r="I27" t="n">
         <v>4479.470293724994</v>
       </c>
       <c r="J27" s="2" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="K27" t="n">
-        <v>1.76</v>
+        <v>-1.3</v>
       </c>
       <c r="L27" t="n">
         <v>6.29</v>
       </c>
       <c r="M27" t="n">
-        <v>1.01</v>
+        <v>2.42</v>
       </c>
       <c r="N27" t="n">
-        <v>2.05</v>
+        <v>2.84</v>
       </c>
       <c r="O27" t="n">
         <v>-4.36</v>
@@ -1989,7 +2312,19 @@
         <v>1</v>
       </c>
       <c r="Q27" t="n">
-        <v>29</v>
+        <v>30</v>
+      </c>
+      <c r="R27" s="3" t="n">
+        <v>45351</v>
+      </c>
+      <c r="S27" t="b">
+        <v>1</v>
+      </c>
+      <c r="T27" t="n">
+        <v>2</v>
+      </c>
+      <c r="U27" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="28">
@@ -2016,19 +2351,19 @@
         <v>6.2</v>
       </c>
       <c r="G28" s="1" t="n">
-        <v>45392.55208333334</v>
+        <v>45394.38541666666</v>
       </c>
       <c r="H28" t="n">
-        <v>4385.05</v>
+        <v>4359.3</v>
       </c>
       <c r="I28" t="n">
         <v>4359.922914657554</v>
       </c>
       <c r="J28" s="2" t="n">
-        <v>37.16666666666666</v>
+        <v>39</v>
       </c>
       <c r="K28" t="n">
-        <v>-2.73</v>
+        <v>-3.3</v>
       </c>
       <c r="L28" t="n">
         <v>3.81</v>
@@ -2046,7 +2381,19 @@
         <v>0</v>
       </c>
       <c r="Q28" t="n">
-        <v>50</v>
+        <v>51</v>
+      </c>
+      <c r="R28" s="3" t="n">
+        <v>45379</v>
+      </c>
+      <c r="S28" t="b">
+        <v>1</v>
+      </c>
+      <c r="T28" t="n">
+        <v>2</v>
+      </c>
+      <c r="U28" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="29">
@@ -2073,19 +2420,19 @@
         <v>5.23</v>
       </c>
       <c r="G29" s="1" t="n">
-        <v>45406.55208333334</v>
+        <v>45407.38541666666</v>
       </c>
       <c r="H29" t="n">
-        <v>4293.3</v>
+        <v>4366.65</v>
       </c>
       <c r="I29" t="n">
         <v>4318.151186978458</v>
       </c>
       <c r="J29" s="2" t="n">
-        <v>12.16666666666667</v>
+        <v>13</v>
       </c>
       <c r="K29" t="n">
-        <v>1.51</v>
+        <v>-0.17</v>
       </c>
       <c r="L29" t="n">
         <v>1.21</v>
@@ -2103,7 +2450,19 @@
         <v>0</v>
       </c>
       <c r="Q29" t="n">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="R29" s="3" t="n">
+        <v>45407</v>
+      </c>
+      <c r="S29" t="b">
+        <v>0</v>
+      </c>
+      <c r="T29" t="n">
+        <v>1</v>
+      </c>
+      <c r="U29" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="30">
@@ -2130,19 +2489,19 @@
         <v>6.05</v>
       </c>
       <c r="G30" s="1" t="n">
-        <v>45463.38541666666</v>
+        <v>45463.55208333334</v>
       </c>
       <c r="H30" t="n">
-        <v>5404.4</v>
+        <v>5376.1</v>
       </c>
       <c r="I30" t="n">
         <v>5382.069444205011</v>
       </c>
       <c r="J30" s="2" t="n">
-        <v>56</v>
+        <v>56.16666666666666</v>
       </c>
       <c r="K30" t="n">
-        <v>23.77</v>
+        <v>23.12</v>
       </c>
       <c r="L30" t="n">
         <v>2.44</v>
@@ -2160,7 +2519,19 @@
         <v>0</v>
       </c>
       <c r="Q30" t="n">
-        <v>76</v>
+        <v>77</v>
+      </c>
+      <c r="R30" s="3" t="n">
+        <v>45442</v>
+      </c>
+      <c r="S30" t="b">
+        <v>1</v>
+      </c>
+      <c r="T30" t="n">
+        <v>2</v>
+      </c>
+      <c r="U30" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="31">
@@ -2187,19 +2558,19 @@
         <v>5.49</v>
       </c>
       <c r="G31" s="1" t="n">
-        <v>45526.55208333334</v>
+        <v>45527.38541666666</v>
       </c>
       <c r="H31" t="n">
-        <v>5209.3</v>
+        <v>5285.5</v>
       </c>
       <c r="I31" t="n">
         <v>5256.806140184935</v>
       </c>
       <c r="J31" s="2" t="n">
-        <v>63</v>
+        <v>63.83333333333334</v>
       </c>
       <c r="K31" t="n">
-        <v>3.1</v>
+        <v>1.69</v>
       </c>
       <c r="L31" t="n">
         <v>3.94</v>
@@ -2217,7 +2588,19 @@
         <v>0</v>
       </c>
       <c r="Q31" t="n">
-        <v>87</v>
+        <v>88</v>
+      </c>
+      <c r="R31" s="3" t="n">
+        <v>45470</v>
+      </c>
+      <c r="S31" t="b">
+        <v>1</v>
+      </c>
+      <c r="T31" t="n">
+        <v>3</v>
+      </c>
+      <c r="U31" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="32">
@@ -2244,28 +2627,28 @@
         <v>5.76</v>
       </c>
       <c r="G32" s="1" t="n">
-        <v>45562.55208333334</v>
+        <v>45565.38541666666</v>
       </c>
       <c r="H32" t="n">
-        <v>5820.95</v>
+        <v>5566.7</v>
       </c>
       <c r="I32" t="n">
         <v>5735.820128873641</v>
       </c>
       <c r="J32" s="2" t="n">
-        <v>35.16666666666666</v>
+        <v>38</v>
       </c>
       <c r="K32" t="n">
-        <v>10.13</v>
+        <v>5.32</v>
       </c>
       <c r="L32" t="n">
         <v>2.81</v>
       </c>
       <c r="M32" t="n">
-        <v>0.96</v>
+        <v>1.29</v>
       </c>
       <c r="N32" t="n">
-        <v>1.2</v>
+        <v>4.04</v>
       </c>
       <c r="O32" t="n">
         <v>0.79</v>
@@ -2274,7 +2657,19 @@
         <v>0</v>
       </c>
       <c r="Q32" t="n">
-        <v>52</v>
+        <v>53</v>
+      </c>
+      <c r="R32" s="3" t="n">
+        <v>45533</v>
+      </c>
+      <c r="S32" t="b">
+        <v>1</v>
+      </c>
+      <c r="T32" t="n">
+        <v>3</v>
+      </c>
+      <c r="U32" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="33">
@@ -2301,19 +2696,19 @@
         <v>7.37</v>
       </c>
       <c r="G33" s="1" t="n">
-        <v>45614.55208333334</v>
+        <v>45615.38541666666</v>
       </c>
       <c r="H33" t="n">
-        <v>4612.25</v>
+        <v>4711.85</v>
       </c>
       <c r="I33" t="n">
         <v>4677.051741589894</v>
       </c>
       <c r="J33" s="2" t="n">
-        <v>49.16666666666666</v>
+        <v>50</v>
       </c>
       <c r="K33" t="n">
-        <v>17.15</v>
+        <v>15.36</v>
       </c>
       <c r="L33" t="n">
         <v>3.22</v>
@@ -2331,7 +2726,19 @@
         <v>1</v>
       </c>
       <c r="Q33" t="n">
-        <v>67</v>
+        <v>68</v>
+      </c>
+      <c r="R33" s="3" t="n">
+        <v>45596</v>
+      </c>
+      <c r="S33" t="b">
+        <v>1</v>
+      </c>
+      <c r="T33" t="n">
+        <v>2</v>
+      </c>
+      <c r="U33" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="34">
@@ -2358,22 +2765,22 @@
         <v>7.05</v>
       </c>
       <c r="G34" s="1" t="n">
-        <v>45629.55208333334</v>
+        <v>45630.38541666666</v>
       </c>
       <c r="H34" t="n">
-        <v>4581.05</v>
+        <v>4527.55</v>
       </c>
       <c r="I34" t="n">
         <v>4552.097132586269</v>
       </c>
       <c r="J34" s="2" t="n">
-        <v>14.16666666666667</v>
+        <v>15</v>
       </c>
       <c r="K34" t="n">
-        <v>-2.78</v>
+        <v>-3.91</v>
       </c>
       <c r="L34" t="n">
-        <v>2.9</v>
+        <v>4.33</v>
       </c>
       <c r="M34" t="n">
         <v>0.66</v>
@@ -2388,7 +2795,19 @@
         <v>0</v>
       </c>
       <c r="Q34" t="n">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="R34" s="3" t="n">
+        <v>45624</v>
+      </c>
+      <c r="S34" t="b">
+        <v>1</v>
+      </c>
+      <c r="T34" t="n">
+        <v>2</v>
+      </c>
+      <c r="U34" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="35">
@@ -2415,19 +2834,19 @@
         <v>5.23</v>
       </c>
       <c r="G35" s="1" t="n">
-        <v>45687.38541666666</v>
+        <v>45687.55208333334</v>
       </c>
       <c r="H35" t="n">
-        <v>4052.3</v>
+        <v>4082.55</v>
       </c>
       <c r="I35" t="n">
         <v>4070.932805342993</v>
       </c>
       <c r="J35" s="2" t="n">
-        <v>57</v>
+        <v>57.16666666666666</v>
       </c>
       <c r="K35" t="n">
-        <v>10.5</v>
+        <v>9.83</v>
       </c>
       <c r="L35" t="n">
         <v>1.81</v>
@@ -2445,7 +2864,19 @@
         <v>0</v>
       </c>
       <c r="Q35" t="n">
-        <v>81</v>
+        <v>82</v>
+      </c>
+      <c r="R35" s="3" t="n">
+        <v>45652</v>
+      </c>
+      <c r="S35" t="b">
+        <v>1</v>
+      </c>
+      <c r="T35" t="n">
+        <v>2</v>
+      </c>
+      <c r="U35" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="36">
@@ -2472,22 +2903,22 @@
         <v>4.77</v>
       </c>
       <c r="G36" s="1" t="n">
-        <v>45698.55208333334</v>
+        <v>45699.38541666666</v>
       </c>
       <c r="H36" t="n">
-        <v>4102.05</v>
+        <v>3977.3</v>
       </c>
       <c r="I36" t="n">
         <v>4053.235978234989</v>
       </c>
       <c r="J36" s="2" t="n">
-        <v>11</v>
+        <v>11.83333333333333</v>
       </c>
       <c r="K36" t="n">
-        <v>0.48</v>
+        <v>-2.58</v>
       </c>
       <c r="L36" t="n">
-        <v>1.24</v>
+        <v>2.63</v>
       </c>
       <c r="M36" t="n">
         <v>0.18</v>
@@ -2502,7 +2933,19 @@
         <v>0</v>
       </c>
       <c r="Q36" t="n">
-        <v>17</v>
+        <v>18</v>
+      </c>
+      <c r="R36" s="3" t="n">
+        <v>45715</v>
+      </c>
+      <c r="S36" t="b">
+        <v>0</v>
+      </c>
+      <c r="T36" t="n">
+        <v>1</v>
+      </c>
+      <c r="U36" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="37">
@@ -2529,19 +2972,19 @@
         <v>8.57</v>
       </c>
       <c r="G37" s="1" t="n">
-        <v>45736.55208333334</v>
+        <v>45737.38541666666</v>
       </c>
       <c r="H37" t="n">
-        <v>3599</v>
+        <v>3670.15</v>
       </c>
       <c r="I37" t="n">
         <v>3659.329939382074</v>
       </c>
       <c r="J37" s="2" t="n">
-        <v>37.16666666666666</v>
+        <v>38</v>
       </c>
       <c r="K37" t="n">
-        <v>9.51</v>
+        <v>7.72</v>
       </c>
       <c r="L37" t="n">
         <v>3.97</v>
@@ -2559,7 +3002,19 @@
         <v>0</v>
       </c>
       <c r="Q37" t="n">
-        <v>52</v>
+        <v>53</v>
+      </c>
+      <c r="R37" s="3" t="n">
+        <v>45715</v>
+      </c>
+      <c r="S37" t="b">
+        <v>1</v>
+      </c>
+      <c r="T37" t="n">
+        <v>2</v>
+      </c>
+      <c r="U37" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="38">
@@ -2586,28 +3041,28 @@
         <v>5.26</v>
       </c>
       <c r="G38" s="1" t="n">
-        <v>45751.55208333334</v>
+        <v>45754.38541666666</v>
       </c>
       <c r="H38" t="n">
-        <v>3662.45</v>
+        <v>3472.2</v>
       </c>
       <c r="I38" t="n">
         <v>3576.909153410081</v>
       </c>
       <c r="J38" s="2" t="n">
-        <v>14.16666666666667</v>
+        <v>17</v>
       </c>
       <c r="K38" t="n">
-        <v>-0.21</v>
+        <v>-5.39</v>
       </c>
       <c r="L38" t="n">
-        <v>2.38</v>
+        <v>8.890000000000001</v>
       </c>
       <c r="M38" t="n">
-        <v>0.52</v>
+        <v>5.01</v>
       </c>
       <c r="N38" t="n">
-        <v>2.2</v>
+        <v>3.77</v>
       </c>
       <c r="O38" t="n">
         <v>0.9399999999999999</v>
@@ -2616,7 +3071,19 @@
         <v>0</v>
       </c>
       <c r="Q38" t="n">
-        <v>18</v>
+        <v>19</v>
+      </c>
+      <c r="R38" s="3" t="n">
+        <v>45743</v>
+      </c>
+      <c r="S38" t="b">
+        <v>1</v>
+      </c>
+      <c r="T38" t="n">
+        <v>2</v>
+      </c>
+      <c r="U38" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="39">
@@ -2643,28 +3110,28 @@
         <v>6.3</v>
       </c>
       <c r="G39" s="1" t="n">
-        <v>45758.55208333334</v>
+        <v>45762.38541666666</v>
       </c>
       <c r="H39" t="n">
-        <v>3660.6</v>
+        <v>3745.7</v>
       </c>
       <c r="I39" t="n">
         <v>3690.935536947646</v>
       </c>
       <c r="J39" s="2" t="n">
-        <v>4.166666666666667</v>
+        <v>8</v>
       </c>
       <c r="K39" t="n">
-        <v>-5.43</v>
+        <v>-7.88</v>
       </c>
       <c r="L39" t="n">
-        <v>6.68</v>
+        <v>8.41</v>
       </c>
       <c r="M39" t="n">
-        <v>2.15</v>
+        <v>2.41</v>
       </c>
       <c r="N39" t="n">
-        <v>1.36</v>
+        <v>4.03</v>
       </c>
       <c r="O39" t="n">
         <v>-3.77</v>
@@ -2673,7 +3140,19 @@
         <v>0</v>
       </c>
       <c r="Q39" t="n">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="R39" s="3" t="n">
+        <v>45771</v>
+      </c>
+      <c r="S39" t="b">
+        <v>0</v>
+      </c>
+      <c r="T39" t="n">
+        <v>1</v>
+      </c>
+      <c r="U39" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="40">
@@ -2700,28 +3179,28 @@
         <v>7.02</v>
       </c>
       <c r="G40" s="1" t="n">
-        <v>45777.55208333334</v>
+        <v>45779.38541666666</v>
       </c>
       <c r="H40" t="n">
-        <v>3825</v>
+        <v>3728.6</v>
       </c>
       <c r="I40" t="n">
         <v>3734.951713560238</v>
       </c>
       <c r="J40" s="2" t="n">
-        <v>15.16666666666667</v>
+        <v>17</v>
       </c>
       <c r="K40" t="n">
-        <v>2.12</v>
+        <v>-0.46</v>
       </c>
       <c r="L40" t="n">
         <v>2.17</v>
       </c>
       <c r="M40" t="n">
-        <v>0.21</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="N40" t="n">
-        <v>2.19</v>
+        <v>2.2</v>
       </c>
       <c r="O40" t="n">
         <v>4.03</v>
@@ -2730,7 +3209,19 @@
         <v>1</v>
       </c>
       <c r="Q40" t="n">
-        <v>22</v>
+        <v>23</v>
+      </c>
+      <c r="R40" s="3" t="n">
+        <v>45771</v>
+      </c>
+      <c r="S40" t="b">
+        <v>1</v>
+      </c>
+      <c r="T40" t="n">
+        <v>2</v>
+      </c>
+      <c r="U40" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="41">
@@ -2757,22 +3248,22 @@
         <v>8.800000000000001</v>
       </c>
       <c r="G41" s="1" t="n">
-        <v>45789.38541666666</v>
+        <v>45789.55208333334</v>
       </c>
       <c r="H41" t="n">
-        <v>3932.9</v>
+        <v>3998</v>
       </c>
       <c r="I41" t="n">
         <v>3977.565064977385</v>
       </c>
       <c r="J41" s="2" t="n">
-        <v>10</v>
+        <v>10.16666666666667</v>
       </c>
       <c r="K41" t="n">
-        <v>-5.48</v>
+        <v>-7.23</v>
       </c>
       <c r="L41" t="n">
-        <v>6.18</v>
+        <v>7.27</v>
       </c>
       <c r="M41" t="n">
         <v>1.89</v>
@@ -2787,7 +3278,19 @@
         <v>0</v>
       </c>
       <c r="Q41" t="n">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="R41" s="3" t="n">
+        <v>45806</v>
+      </c>
+      <c r="S41" t="b">
+        <v>0</v>
+      </c>
+      <c r="T41" t="n">
+        <v>1</v>
+      </c>
+      <c r="U41" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="42">
@@ -2814,19 +3317,19 @@
         <v>6.18</v>
       </c>
       <c r="G42" s="1" t="n">
-        <v>45813.38541666666</v>
+        <v>45813.55208333334</v>
       </c>
       <c r="H42" t="n">
-        <v>4202.4</v>
+        <v>4177</v>
       </c>
       <c r="I42" t="n">
         <v>4179.544646417477</v>
       </c>
       <c r="J42" s="2" t="n">
-        <v>23.83333333333333</v>
+        <v>24</v>
       </c>
       <c r="K42" t="n">
-        <v>5.11</v>
+        <v>4.48</v>
       </c>
       <c r="L42" t="n">
         <v>1.63</v>
@@ -2844,7 +3347,19 @@
         <v>0</v>
       </c>
       <c r="Q42" t="n">
-        <v>36</v>
+        <v>37</v>
+      </c>
+      <c r="R42" s="3" t="n">
+        <v>45806</v>
+      </c>
+      <c r="S42" t="b">
+        <v>1</v>
+      </c>
+      <c r="T42" t="n">
+        <v>2</v>
+      </c>
+      <c r="U42" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="43">
@@ -2871,22 +3386,22 @@
         <v>4.12</v>
       </c>
       <c r="G43" s="1" t="n">
-        <v>45817.55208333334</v>
+        <v>45818.38541666666</v>
       </c>
       <c r="H43" t="n">
-        <v>4342</v>
+        <v>4391</v>
       </c>
       <c r="I43" t="n">
         <v>4349.12283582586</v>
       </c>
       <c r="J43" s="2" t="n">
-        <v>4</v>
+        <v>4.833333333333333</v>
       </c>
       <c r="K43" t="n">
-        <v>-3.95</v>
+        <v>-5.12</v>
       </c>
       <c r="L43" t="n">
-        <v>4.38</v>
+        <v>5.15</v>
       </c>
       <c r="M43" t="n">
         <v>0.67</v>
@@ -2901,7 +3416,19 @@
         <v>0</v>
       </c>
       <c r="Q43" t="n">
-        <v>5</v>
+        <v>6</v>
+      </c>
+      <c r="R43" s="3" t="n">
+        <v>45834</v>
+      </c>
+      <c r="S43" t="b">
+        <v>0</v>
+      </c>
+      <c r="T43" t="n">
+        <v>1</v>
+      </c>
+      <c r="U43" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="44">
@@ -2928,19 +3455,19 @@
         <v>4.5</v>
       </c>
       <c r="G44" s="1" t="n">
-        <v>45831.38541666666</v>
+        <v>45831.55208333334</v>
       </c>
       <c r="H44" t="n">
-        <v>4268</v>
+        <v>4247.2</v>
       </c>
       <c r="I44" t="n">
         <v>4248.328649971256</v>
       </c>
       <c r="J44" s="2" t="n">
-        <v>13</v>
+        <v>13.16666666666667</v>
       </c>
       <c r="K44" t="n">
-        <v>-2.8</v>
+        <v>-3.27</v>
       </c>
       <c r="L44" t="n">
         <v>4.24</v>
@@ -2958,7 +3485,19 @@
         <v>0</v>
       </c>
       <c r="Q44" t="n">
-        <v>19</v>
+        <v>20</v>
+      </c>
+      <c r="R44" s="3" t="n">
+        <v>45834</v>
+      </c>
+      <c r="S44" t="b">
+        <v>0</v>
+      </c>
+      <c r="T44" t="n">
+        <v>1</v>
+      </c>
+      <c r="U44" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="45">
@@ -2985,28 +3524,28 @@
         <v>4.88</v>
       </c>
       <c r="G45" s="1" t="n">
-        <v>45852.55208333334</v>
+        <v>45853.38541666666</v>
       </c>
       <c r="H45" t="n">
-        <v>4244.8</v>
+        <v>4441.6</v>
       </c>
       <c r="I45" t="n">
         <v>4379.439523840229</v>
       </c>
       <c r="J45" s="2" t="n">
-        <v>21</v>
+        <v>21.83333333333333</v>
       </c>
       <c r="K45" t="n">
-        <v>0.06</v>
+        <v>-4.58</v>
       </c>
       <c r="L45" t="n">
-        <v>3</v>
+        <v>4.76</v>
       </c>
       <c r="M45" t="n">
         <v>1.31</v>
       </c>
       <c r="N45" t="n">
-        <v>1.89</v>
+        <v>5.07</v>
       </c>
       <c r="O45" t="n">
         <v>-1.94</v>
@@ -3015,7 +3554,19 @@
         <v>0</v>
       </c>
       <c r="Q45" t="n">
-        <v>31</v>
+        <v>32</v>
+      </c>
+      <c r="R45" s="3" t="n">
+        <v>45834</v>
+      </c>
+      <c r="S45" t="b">
+        <v>1</v>
+      </c>
+      <c r="T45" t="n">
+        <v>2</v>
+      </c>
+      <c r="U45" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="46">
@@ -3042,28 +3593,28 @@
         <v>6.47</v>
       </c>
       <c r="G46" s="1" t="n">
-        <v>45862.55208333334</v>
+        <v>45863.38541666666</v>
       </c>
       <c r="H46" t="n">
-        <v>4301</v>
+        <v>4222.6</v>
       </c>
       <c r="I46" t="n">
         <v>4267.605304858768</v>
       </c>
       <c r="J46" s="2" t="n">
-        <v>9.166666666666666</v>
+        <v>10</v>
       </c>
       <c r="K46" t="n">
-        <v>-3.17</v>
+        <v>-4.93</v>
       </c>
       <c r="L46" t="n">
-        <v>4.2</v>
+        <v>5.55</v>
       </c>
       <c r="M46" t="n">
         <v>1.33</v>
       </c>
       <c r="N46" t="n">
-        <v>1.61</v>
+        <v>1.85</v>
       </c>
       <c r="O46" t="n">
         <v>5.07</v>
@@ -3072,7 +3623,19 @@
         <v>1</v>
       </c>
       <c r="Q46" t="n">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="R46" s="3" t="n">
+        <v>45869</v>
+      </c>
+      <c r="S46" t="b">
+        <v>0</v>
+      </c>
+      <c r="T46" t="n">
+        <v>1</v>
+      </c>
+      <c r="U46" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="47">
@@ -3099,28 +3662,28 @@
         <v>4.99</v>
       </c>
       <c r="G47" s="1" t="n">
-        <v>45870.55208333334</v>
+        <v>45873.38541666666</v>
       </c>
       <c r="H47" t="n">
-        <v>4309</v>
+        <v>4456.5</v>
       </c>
       <c r="I47" t="n">
         <v>4402.510629777626</v>
       </c>
       <c r="J47" s="2" t="n">
-        <v>7.166666666666667</v>
+        <v>10</v>
       </c>
       <c r="K47" t="n">
-        <v>-2.05</v>
+        <v>-5.54</v>
       </c>
       <c r="L47" t="n">
-        <v>2.65</v>
+        <v>5.86</v>
       </c>
       <c r="M47" t="n">
-        <v>0.08</v>
+        <v>0.16</v>
       </c>
       <c r="N47" t="n">
-        <v>1.67</v>
+        <v>5.36</v>
       </c>
       <c r="O47" t="n">
         <v>-1.85</v>
@@ -3129,7 +3692,19 @@
         <v>0</v>
       </c>
       <c r="Q47" t="n">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="R47" s="3" t="n">
+        <v>45869</v>
+      </c>
+      <c r="S47" t="b">
+        <v>1</v>
+      </c>
+      <c r="T47" t="n">
+        <v>2</v>
+      </c>
+      <c r="U47" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="48">
@@ -3156,28 +3731,28 @@
         <v>6.27</v>
       </c>
       <c r="G48" s="1" t="n">
-        <v>45964.55208333334</v>
+        <v>45965.38541666666</v>
       </c>
       <c r="H48" t="n">
-        <v>5532</v>
+        <v>5315.5</v>
       </c>
       <c r="I48" t="n">
         <v>5458.427693858033</v>
       </c>
       <c r="J48" s="2" t="n">
-        <v>91.16666666666667</v>
+        <v>92</v>
       </c>
       <c r="K48" t="n">
-        <v>24.13</v>
+        <v>19.28</v>
       </c>
       <c r="L48" t="n">
         <v>3.29</v>
       </c>
       <c r="M48" t="n">
-        <v>0.9</v>
+        <v>1.03</v>
       </c>
       <c r="N48" t="n">
-        <v>2.23</v>
+        <v>4.19</v>
       </c>
       <c r="O48" t="n">
         <v>5.36</v>
@@ -3186,7 +3761,19 @@
         <v>1</v>
       </c>
       <c r="Q48" t="n">
-        <v>123</v>
+        <v>124</v>
+      </c>
+      <c r="R48" s="3" t="n">
+        <v>45897</v>
+      </c>
+      <c r="S48" t="b">
+        <v>1</v>
+      </c>
+      <c r="T48" t="n">
+        <v>4</v>
+      </c>
+      <c r="U48" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="49">
@@ -3213,22 +3800,22 @@
         <v>5.98</v>
       </c>
       <c r="G49" s="1" t="n">
-        <v>45973.38541666666</v>
+        <v>45973.55208333334</v>
       </c>
       <c r="H49" t="n">
-        <v>5522</v>
+        <v>5530</v>
       </c>
       <c r="I49" t="n">
         <v>5529.080098376125</v>
       </c>
       <c r="J49" s="2" t="n">
-        <v>8</v>
+        <v>8.166666666666666</v>
       </c>
       <c r="K49" t="n">
-        <v>-3.88</v>
+        <v>-4.04</v>
       </c>
       <c r="L49" t="n">
-        <v>3.95</v>
+        <v>4.54</v>
       </c>
       <c r="M49" t="n">
         <v>0.99</v>
@@ -3243,7 +3830,19 @@
         <v>1</v>
       </c>
       <c r="Q49" t="n">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="R49" s="3" t="n">
+        <v>45986</v>
+      </c>
+      <c r="S49" t="b">
+        <v>0</v>
+      </c>
+      <c r="T49" t="n">
+        <v>1</v>
+      </c>
+      <c r="U49" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="50">
@@ -3270,19 +3869,19 @@
         <v>3.81</v>
       </c>
       <c r="G50" s="1" t="n">
-        <v>45999.55208333334</v>
+        <v>46000.38541666666</v>
       </c>
       <c r="H50" t="n">
-        <v>6152</v>
+        <v>6029</v>
       </c>
       <c r="I50" t="n">
         <v>6140.186686166919</v>
       </c>
       <c r="J50" s="2" t="n">
-        <v>26</v>
+        <v>26.83333333333333</v>
       </c>
       <c r="K50" t="n">
-        <v>11.25</v>
+        <v>9.02</v>
       </c>
       <c r="L50" t="n">
         <v>1.22</v>
@@ -3300,7 +3899,19 @@
         <v>0</v>
       </c>
       <c r="Q50" t="n">
-        <v>37</v>
+        <v>38</v>
+      </c>
+      <c r="R50" s="3" t="n">
+        <v>45986</v>
+      </c>
+      <c r="S50" t="b">
+        <v>1</v>
+      </c>
+      <c r="T50" t="n">
+        <v>2</v>
+      </c>
+      <c r="U50" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="51">
@@ -3327,19 +3938,19 @@
         <v>5.07</v>
       </c>
       <c r="G51" s="1" t="n">
-        <v>46022.55208333334</v>
+        <v>46023.38541666666</v>
       </c>
       <c r="H51" t="n">
-        <v>5762.5</v>
+        <v>5797.5</v>
       </c>
       <c r="I51" t="n">
         <v>5766.714286985653</v>
       </c>
       <c r="J51" s="2" t="n">
-        <v>22.16666666666667</v>
+        <v>23</v>
       </c>
       <c r="K51" t="n">
-        <v>4.42</v>
+        <v>3.84</v>
       </c>
       <c r="L51" t="n">
         <v>2.24</v>
@@ -3357,7 +3968,19 @@
         <v>0</v>
       </c>
       <c r="Q51" t="n">
-        <v>32</v>
+        <v>33</v>
+      </c>
+      <c r="R51" s="3" t="n">
+        <v>46021</v>
+      </c>
+      <c r="S51" t="b">
+        <v>1</v>
+      </c>
+      <c r="T51" t="n">
+        <v>2</v>
+      </c>
+      <c r="U51" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="52">
@@ -3384,19 +4007,19 @@
         <v>4.09</v>
       </c>
       <c r="G52" s="1" t="n">
-        <v>46031.38541666666</v>
+        <v>46031.55208333334</v>
       </c>
       <c r="H52" t="n">
-        <v>5786</v>
+        <v>5779</v>
       </c>
       <c r="I52" t="n">
         <v>5781.755181768203</v>
       </c>
       <c r="J52" s="2" t="n">
-        <v>8</v>
+        <v>8.166666666666666</v>
       </c>
       <c r="K52" t="n">
-        <v>-0.2</v>
+        <v>-0.32</v>
       </c>
       <c r="L52" t="n">
         <v>1.16</v>
@@ -3414,7 +4037,19 @@
         <v>0</v>
       </c>
       <c r="Q52" t="n">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="R52" s="3" t="n">
+        <v>46049</v>
+      </c>
+      <c r="S52" t="b">
+        <v>0</v>
+      </c>
+      <c r="T52" t="n">
+        <v>1</v>
+      </c>
+      <c r="U52" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="53">
@@ -3441,28 +4076,28 @@
         <v>4.36</v>
       </c>
       <c r="G53" s="1" t="n">
-        <v>46055.55208333334</v>
+        <v>46056.38541666666</v>
       </c>
       <c r="H53" t="n">
-        <v>5635.5</v>
+        <v>5695.5</v>
       </c>
       <c r="I53" t="n">
         <v>5653.565170210467</v>
       </c>
       <c r="J53" s="2" t="n">
-        <v>24</v>
+        <v>24.83333333333333</v>
       </c>
       <c r="K53" t="n">
-        <v>2.48</v>
+        <v>1.44</v>
       </c>
       <c r="L53" t="n">
         <v>1.14</v>
       </c>
       <c r="M53" t="n">
-        <v>1.01</v>
+        <v>1.75</v>
       </c>
       <c r="N53" t="n">
-        <v>2.41</v>
+        <v>2.47</v>
       </c>
       <c r="O53" t="n">
         <v>-1.13</v>
@@ -3471,7 +4106,19 @@
         <v>0</v>
       </c>
       <c r="Q53" t="n">
-        <v>31</v>
+        <v>32</v>
+      </c>
+      <c r="R53" s="3" t="n">
+        <v>46049</v>
+      </c>
+      <c r="S53" t="b">
+        <v>1</v>
+      </c>
+      <c r="T53" t="n">
+        <v>2</v>
+      </c>
+      <c r="U53" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="54">
@@ -3498,22 +4145,22 @@
         <v>6.05</v>
       </c>
       <c r="G54" s="1" t="n">
-        <v>46066.55208333334</v>
+        <v>46069.38541666666</v>
       </c>
       <c r="H54" t="n">
-        <v>5569.5</v>
+        <v>5490</v>
       </c>
       <c r="I54" t="n">
         <v>5491.083124199489</v>
       </c>
       <c r="J54" s="2" t="n">
-        <v>10.16666666666667</v>
+        <v>13</v>
       </c>
       <c r="K54" t="n">
-        <v>-2.21</v>
+        <v>-3.61</v>
       </c>
       <c r="L54" t="n">
-        <v>2.62</v>
+        <v>4.15</v>
       </c>
       <c r="M54" t="n">
         <v>1.03</v>
@@ -3528,7 +4175,19 @@
         <v>0</v>
       </c>
       <c r="Q54" t="n">
-        <v>18</v>
+        <v>19</v>
+      </c>
+      <c r="R54" s="3" t="n">
+        <v>46077</v>
+      </c>
+      <c r="S54" t="b">
+        <v>0</v>
+      </c>
+      <c r="T54" t="n">
+        <v>1</v>
+      </c>
+      <c r="U54" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="55">
@@ -3555,28 +4214,28 @@
         <v>6.83</v>
       </c>
       <c r="G55" s="1" t="n">
-        <v>46077.55208333334</v>
+        <v>46078.38541666666</v>
       </c>
       <c r="H55" t="n">
-        <v>5520</v>
+        <v>5721</v>
       </c>
       <c r="I55" t="n">
         <v>5698.729373659859</v>
       </c>
       <c r="J55" s="2" t="n">
-        <v>8.166666666666666</v>
+        <v>9</v>
       </c>
       <c r="K55" t="n">
-        <v>-0.55</v>
+        <v>-4.21</v>
       </c>
       <c r="L55" t="n">
-        <v>2.81</v>
+        <v>6.38</v>
       </c>
       <c r="M55" t="n">
         <v>0.85</v>
       </c>
       <c r="N55" t="n">
-        <v>1.5</v>
+        <v>3.99</v>
       </c>
       <c r="O55" t="n">
         <v>-1.56</v>
@@ -3585,7 +4244,19 @@
         <v>0</v>
       </c>
       <c r="Q55" t="n">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="R55" s="3" t="n">
+        <v>46077</v>
+      </c>
+      <c r="S55" t="b">
+        <v>1</v>
+      </c>
+      <c r="T55" t="n">
+        <v>2</v>
+      </c>
+      <c r="U55" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="56">
@@ -3612,22 +4283,22 @@
         <v>6.76</v>
       </c>
       <c r="G56" s="1" t="n">
-        <v>46087.55208333334</v>
+        <v>46090.38541666666</v>
       </c>
       <c r="H56" t="n">
-        <v>5525</v>
+        <v>5435</v>
       </c>
       <c r="I56" t="n">
         <v>5459.038218975593</v>
       </c>
       <c r="J56" s="2" t="n">
-        <v>9.166666666666666</v>
+        <v>12</v>
       </c>
       <c r="K56" t="n">
-        <v>-3.43</v>
+        <v>-5</v>
       </c>
       <c r="L56" t="n">
-        <v>5.13</v>
+        <v>6.7</v>
       </c>
       <c r="M56" t="n">
         <v>2.62</v>
@@ -3642,7 +4313,19 @@
         <v>0</v>
       </c>
       <c r="Q56" t="n">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="R56" s="3" t="n">
+        <v>46111</v>
+      </c>
+      <c r="S56" t="b">
+        <v>0</v>
+      </c>
+      <c r="T56" t="n">
+        <v>1</v>
+      </c>
+      <c r="U56" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="57">
@@ -3669,19 +4352,19 @@
         <v>5.51</v>
       </c>
       <c r="G57" s="1" t="n">
-        <v>46121.55208333334</v>
+        <v>46122.38541666666</v>
       </c>
       <c r="H57" t="n">
-        <v>5279.5</v>
+        <v>5461</v>
       </c>
       <c r="I57" t="n">
         <v>5368.898953994649</v>
       </c>
       <c r="J57" s="2" t="n">
-        <v>31.16666666666667</v>
+        <v>32</v>
       </c>
       <c r="K57" t="n">
-        <v>2.86</v>
+        <v>-0.48</v>
       </c>
       <c r="L57" t="n">
         <v>6.09</v>
@@ -3699,7 +4382,19 @@
         <v>0</v>
       </c>
       <c r="Q57" t="n">
-        <v>42</v>
+        <v>43</v>
+      </c>
+      <c r="R57" s="3" t="n">
+        <v>46111</v>
+      </c>
+      <c r="S57" t="b">
+        <v>1</v>
+      </c>
+      <c r="T57" t="n">
+        <v>2</v>
+      </c>
+      <c r="U57" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="58">
@@ -3726,22 +4421,22 @@
         <v>8.460000000000001</v>
       </c>
       <c r="G58" s="1" t="n">
-        <v>46134.55208333334</v>
+        <v>46135.38541666666</v>
       </c>
       <c r="H58" t="n">
-        <v>5190</v>
+        <v>5032.5</v>
       </c>
       <c r="I58" t="n">
         <v>5092.045399745274</v>
       </c>
       <c r="J58" s="2" t="n">
-        <v>12.16666666666667</v>
+        <v>13</v>
       </c>
       <c r="K58" t="n">
-        <v>-4.96</v>
+        <v>-7.85</v>
       </c>
       <c r="L58" t="n">
-        <v>6.07</v>
+        <v>8.02</v>
       </c>
       <c r="M58" t="n">
         <v>2.43</v>
@@ -3756,7 +4451,19 @@
         <v>0</v>
       </c>
       <c r="Q58" t="n">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="R58" s="3" t="n">
+        <v>46140</v>
+      </c>
+      <c r="S58" t="b">
+        <v>0</v>
+      </c>
+      <c r="T58" t="n">
+        <v>1</v>
+      </c>
+      <c r="U58" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="59">
@@ -3783,28 +4490,28 @@
         <v>6.77</v>
       </c>
       <c r="G59" s="1" t="n">
-        <v>46148.55208333334</v>
+        <v>46149.38541666666</v>
       </c>
       <c r="H59" t="n">
-        <v>5180</v>
+        <v>5445</v>
       </c>
       <c r="I59" t="n">
         <v>5217.300662390916</v>
       </c>
       <c r="J59" s="2" t="n">
-        <v>13.16666666666667</v>
+        <v>14</v>
       </c>
       <c r="K59" t="n">
-        <v>-2.93</v>
+        <v>-8.199999999999999</v>
       </c>
       <c r="L59" t="n">
-        <v>4.94</v>
+        <v>8.460000000000001</v>
       </c>
       <c r="M59" t="n">
         <v>2.2</v>
       </c>
       <c r="N59" t="n">
-        <v>1.49</v>
+        <v>3.4</v>
       </c>
       <c r="O59" t="n">
         <v>-3.01</v>
@@ -3813,7 +4520,19 @@
         <v>0</v>
       </c>
       <c r="Q59" t="n">
-        <v>18</v>
+        <v>19</v>
+      </c>
+      <c r="R59" s="3" t="n">
+        <v>46140</v>
+      </c>
+      <c r="S59" t="b">
+        <v>1</v>
+      </c>
+      <c r="T59" t="n">
+        <v>2</v>
+      </c>
+      <c r="U59" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="60">
@@ -3840,22 +4559,22 @@
         <v>9.48</v>
       </c>
       <c r="G60" s="1" t="n">
-        <v>46155.38541666666</v>
+        <v>46155.55208333334</v>
       </c>
       <c r="H60" t="n">
-        <v>5045</v>
+        <v>4995</v>
       </c>
       <c r="I60" t="n">
         <v>5000.468952133172</v>
       </c>
       <c r="J60" s="2" t="n">
-        <v>6</v>
+        <v>6.166666666666667</v>
       </c>
       <c r="K60" t="n">
-        <v>-7.35</v>
+        <v>-8.26</v>
       </c>
       <c r="L60" t="n">
-        <v>8.1</v>
+        <v>8.6</v>
       </c>
       <c r="M60" t="n">
         <v>1.17</v>
@@ -3870,7 +4589,19 @@
         <v>0</v>
       </c>
       <c r="Q60" t="n">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="R60" s="3" t="n">
+        <v>46168</v>
+      </c>
+      <c r="S60" t="b">
+        <v>0</v>
+      </c>
+      <c r="T60" t="n">
+        <v>1</v>
+      </c>
+      <c r="U60" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="61">
@@ -3897,19 +4628,19 @@
         <v>7.2</v>
       </c>
       <c r="G61" s="1" t="n">
-        <v>46185.55208333334</v>
+        <v>46188.38541666666</v>
       </c>
       <c r="H61" t="n">
-        <v>4961</v>
+        <v>5038.4</v>
       </c>
       <c r="I61" t="n">
         <v>5022.901746113441</v>
       </c>
       <c r="J61" s="2" t="n">
-        <v>30</v>
+        <v>32.83333333333334</v>
       </c>
       <c r="K61" t="n">
-        <v>0.68</v>
+        <v>-0.87</v>
       </c>
       <c r="L61" t="n">
         <v>2.9</v>
@@ -3927,7 +4658,19 @@
         <v>0</v>
       </c>
       <c r="Q61" t="n">
-        <v>43</v>
+        <v>44</v>
+      </c>
+      <c r="R61" s="3" t="n">
+        <v>46168</v>
+      </c>
+      <c r="S61" t="b">
+        <v>1</v>
+      </c>
+      <c r="T61" t="n">
+        <v>2</v>
+      </c>
+      <c r="U61" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="62">
@@ -3954,25 +4697,25 @@
         <v>4.83</v>
       </c>
       <c r="G62" s="1" t="n">
-        <v>46198.55208333334</v>
+        <v>46202.38541666666</v>
       </c>
       <c r="H62" t="n">
-        <v>4905</v>
+        <v>4796.8</v>
       </c>
       <c r="I62" t="n">
         <v>4817.467203393331</v>
       </c>
       <c r="J62" s="2" t="n">
-        <v>10.16666666666667</v>
+        <v>14</v>
       </c>
       <c r="K62" t="n">
-        <v>-2.65</v>
+        <v>-4.8</v>
       </c>
       <c r="L62" t="n">
-        <v>3.2</v>
+        <v>4.83</v>
       </c>
       <c r="M62" t="n">
-        <v>0.3</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="N62" t="n">
         <v>1.85</v>
@@ -3984,7 +4727,19 @@
         <v>0</v>
       </c>
       <c r="Q62" t="n">
-        <v>18</v>
+        <v>19</v>
+      </c>
+      <c r="R62" s="3" t="n">
+        <v>46203</v>
+      </c>
+      <c r="S62" t="b">
+        <v>0</v>
+      </c>
+      <c r="T62" t="n">
+        <v>1</v>
+      </c>
+      <c r="U62" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="63">
@@ -4011,22 +4766,22 @@
         <v>6.53</v>
       </c>
       <c r="G63" s="1" t="n">
-        <v>46224.38541666666</v>
+        <v>46224.55208333334</v>
       </c>
       <c r="H63" t="n">
-        <v>5007.5</v>
+        <v>5035</v>
       </c>
       <c r="I63" t="n">
         <v>5026.815963690902</v>
       </c>
       <c r="J63" s="2" t="n">
-        <v>22</v>
+        <v>22.16666666666667</v>
       </c>
       <c r="K63" t="n">
-        <v>-4.39</v>
+        <v>-4.97</v>
       </c>
       <c r="L63" t="n">
-        <v>4.86</v>
+        <v>5.42</v>
       </c>
       <c r="M63" t="n">
         <v>1.13</v>
@@ -4041,7 +4796,19 @@
         <v>0</v>
       </c>
       <c r="Q63" t="n">
-        <v>33</v>
+        <v>34</v>
+      </c>
+      <c r="R63" s="3" t="n">
+        <v>46203</v>
+      </c>
+      <c r="S63" t="b">
+        <v>1</v>
+      </c>
+      <c r="T63" t="n">
+        <v>2</v>
+      </c>
+      <c r="U63" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="64">
@@ -4068,19 +4835,19 @@
         <v>3.37</v>
       </c>
       <c r="G64" s="1" t="n">
-        <v>46260.55208333334</v>
+        <v>46261.38541666666</v>
       </c>
       <c r="H64" t="n">
-        <v>5647</v>
+        <v>5552</v>
       </c>
       <c r="I64" t="n">
         <v>5607.880443409612</v>
       </c>
       <c r="J64" s="2" t="n">
-        <v>36</v>
+        <v>36.83333333333334</v>
       </c>
       <c r="K64" t="n">
-        <v>12.15</v>
+        <v>10.27</v>
       </c>
       <c r="L64" t="n">
         <v>1.28</v>
@@ -4098,7 +4865,19 @@
         <v>0</v>
       </c>
       <c r="Q64" t="n">
-        <v>53</v>
+        <v>54</v>
+      </c>
+      <c r="R64" s="3" t="n">
+        <v>46231</v>
+      </c>
+      <c r="S64" t="b">
+        <v>1</v>
+      </c>
+      <c r="T64" t="n">
+        <v>3</v>
+      </c>
+      <c r="U64" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="65">
@@ -4125,28 +4904,28 @@
         <v>4.18</v>
       </c>
       <c r="G65" s="1" t="n">
-        <v>46309.55208333334</v>
+        <v>46310.38541666666</v>
       </c>
       <c r="H65" t="n">
-        <v>5015</v>
+        <v>5173.5</v>
       </c>
       <c r="I65" t="n">
         <v>5124.967262804603</v>
       </c>
       <c r="J65" s="2" t="n">
-        <v>48.16666666666666</v>
+        <v>49</v>
       </c>
       <c r="K65" t="n">
-        <v>9.67</v>
+        <v>6.82</v>
       </c>
       <c r="L65" t="n">
         <v>1.93</v>
       </c>
       <c r="M65" t="n">
-        <v>0.95</v>
+        <v>2.19</v>
       </c>
       <c r="N65" t="n">
-        <v>1.83</v>
+        <v>3.33</v>
       </c>
       <c r="O65" t="n">
         <v>-1.72</v>
@@ -4155,7 +4934,19 @@
         <v>0</v>
       </c>
       <c r="Q65" t="n">
-        <v>66</v>
+        <v>67</v>
+      </c>
+      <c r="R65" s="3" t="n">
+        <v>46294</v>
+      </c>
+      <c r="S65" t="b">
+        <v>1</v>
+      </c>
+      <c r="T65" t="n">
+        <v>2</v>
+      </c>
+      <c r="U65" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="66">
@@ -4182,28 +4973,28 @@
         <v>6.23</v>
       </c>
       <c r="G66" s="1" t="n">
-        <v>46317.55208333334</v>
+        <v>46318.38541666666</v>
       </c>
       <c r="H66" t="n">
-        <v>5118</v>
+        <v>5001</v>
       </c>
       <c r="I66" t="n">
         <v>5016.153779838164</v>
       </c>
       <c r="J66" s="2" t="n">
-        <v>7.166666666666667</v>
+        <v>8</v>
       </c>
       <c r="K66" t="n">
-        <v>-1.07</v>
+        <v>-3.33</v>
       </c>
       <c r="L66" t="n">
-        <v>2.67</v>
+        <v>3.46</v>
       </c>
       <c r="M66" t="n">
         <v>0.48</v>
       </c>
       <c r="N66" t="n">
-        <v>1.54</v>
+        <v>1.78</v>
       </c>
       <c r="O66" t="n">
         <v>3.33</v>
@@ -4212,7 +5003,19 @@
         <v>0</v>
       </c>
       <c r="Q66" t="n">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="R66" s="3" t="n">
+        <v>46322</v>
+      </c>
+      <c r="S66" t="b">
+        <v>0</v>
+      </c>
+      <c r="T66" t="n">
+        <v>1</v>
+      </c>
+      <c r="U66" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="67">
@@ -4239,22 +5042,22 @@
         <v>7.81</v>
       </c>
       <c r="G67" s="1" t="n">
-        <v>46323.38541666666</v>
+        <v>46323.55208333334</v>
       </c>
       <c r="H67" t="n">
-        <v>5308</v>
+        <v>5348.5</v>
       </c>
       <c r="I67" t="n">
         <v>5326.899368105123</v>
       </c>
       <c r="J67" s="2" t="n">
-        <v>5</v>
+        <v>5.166666666666667</v>
       </c>
       <c r="K67" t="n">
-        <v>-6.14</v>
+        <v>-6.95</v>
       </c>
       <c r="L67" t="n">
-        <v>6.84</v>
+        <v>7.16</v>
       </c>
       <c r="M67" t="n">
         <v>1.35</v>
@@ -4269,7 +5072,19 @@
         <v>0</v>
       </c>
       <c r="Q67" t="n">
-        <v>7</v>
+        <v>8</v>
+      </c>
+      <c r="R67" s="3" t="n">
+        <v>46322</v>
+      </c>
+      <c r="S67" t="b">
+        <v>1</v>
+      </c>
+      <c r="T67" t="n">
+        <v>2</v>
+      </c>
+      <c r="U67" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="68">
@@ -4320,6 +5135,12 @@
       <c r="Q68" t="n">
         <v>1</v>
       </c>
+      <c r="R68" s="3" t="n">
+        <v>46350</v>
+      </c>
+      <c r="S68" t="inlineStr"/>
+      <c r="T68" t="inlineStr"/>
+      <c r="U68" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -6422,7 +7243,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>25.3</v>
+        <v>26.5</v>
       </c>
     </row>
     <row r="6">
@@ -6432,7 +7253,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>19.7</v>
+        <v>21</v>
       </c>
     </row>
     <row r="7">
@@ -6442,7 +7263,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>91.2</v>
+        <v>92</v>
       </c>
     </row>
     <row r="8">
@@ -6452,7 +7273,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2.2</v>
+        <v>4.8</v>
       </c>
     </row>
     <row r="9">
@@ -6462,7 +7283,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>36.9</v>
+        <v>38</v>
       </c>
     </row>
     <row r="10">
@@ -6472,7 +7293,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>52.6</v>
+        <v>53.1</v>
       </c>
     </row>
     <row r="11">
@@ -6482,7 +7303,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="12">
@@ -6492,7 +7313,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="13">
@@ -6502,7 +7323,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>65.2</v>
+        <v>63.6</v>
       </c>
     </row>
     <row r="14">
@@ -6512,7 +7333,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>3.1</v>
+        <v>0.76</v>
       </c>
     </row>
     <row r="15">
@@ -6522,7 +7343,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>4.7</v>
+        <v>2.24</v>
       </c>
     </row>
     <row r="16">
@@ -6532,7 +7353,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1.5</v>
+        <v>-0.72</v>
       </c>
     </row>
     <row r="17">
@@ -6542,7 +7363,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>24.13</v>
+        <v>23.12</v>
       </c>
     </row>
     <row r="18">
@@ -6552,7 +7373,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>54.5</v>
+        <v>37.9</v>
       </c>
     </row>
     <row r="19">
@@ -6562,7 +7383,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>3.49</v>
+        <v>4.28</v>
       </c>
     </row>
     <row r="20">
@@ -6572,7 +7393,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>3.06</v>
+        <v>3.96</v>
       </c>
     </row>
     <row r="21">
@@ -6582,7 +7403,7 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>8.1</v>
+        <v>10.66</v>
       </c>
     </row>
     <row r="22">
@@ -6592,7 +7413,7 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>12</v>
+        <v>22</v>
       </c>
     </row>
     <row r="23">
@@ -6602,7 +7423,7 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="24">
@@ -6612,7 +7433,7 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1.29</v>
+        <v>1.46</v>
       </c>
     </row>
     <row r="25">
@@ -6622,7 +7443,7 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>4.8</v>
+        <v>5.01</v>
       </c>
     </row>
     <row r="26">
@@ -6632,7 +7453,7 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>2.48</v>
+        <v>3.17</v>
       </c>
     </row>
     <row r="27">
@@ -6652,7 +7473,7 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>3</v>
+        <v>13</v>
       </c>
     </row>
     <row r="29">
